--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104461_W1.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104461_W1.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>G. SHERMADINI</t>
+          <t>J. FERNANDEZ</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.7784</v>
+        <v>8.250500000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>10.2415</v>
+        <v>6.931</v>
       </c>
       <c r="F2" t="n">
-        <v>-2.4631</v>
+        <v>1.3195</v>
       </c>
       <c r="G2" t="n">
-        <v>2.1135</v>
+        <v>3.6654</v>
       </c>
       <c r="H2" t="n">
-        <v>1.9295</v>
+        <v>1.7265</v>
       </c>
       <c r="I2" t="n">
-        <v>0.184</v>
+        <v>1.9389</v>
       </c>
       <c r="J2" t="n">
-        <v>4.7291</v>
+        <v>4.0359</v>
       </c>
       <c r="K2" t="n">
-        <v>3.3483</v>
+        <v>1.713</v>
       </c>
       <c r="L2" t="n">
-        <v>1.3807</v>
+        <v>2.3229</v>
       </c>
       <c r="M2" t="n">
-        <v>-2.6155</v>
+        <v>-0.3704</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.4188</v>
+        <v>0.0135</v>
       </c>
       <c r="O2" t="n">
-        <v>-1.1967</v>
+        <v>-0.384</v>
       </c>
       <c r="P2" t="n">
-        <v>0.2268</v>
+        <v>1.8211</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.361</v>
+        <v>-0.2276</v>
       </c>
       <c r="R2" t="n">
-        <v>1.5878</v>
+        <v>2.0487</v>
       </c>
       <c r="S2" t="n">
-        <v>2.5457</v>
+        <v>0.9721</v>
       </c>
       <c r="T2" t="n">
-        <v>2.8884</v>
+        <v>0.2413</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.3427</v>
+        <v>0.7308</v>
       </c>
       <c r="V2" t="n">
-        <v>2.8924</v>
+        <v>1.792</v>
       </c>
       <c r="W2" t="n">
-        <v>3.9851</v>
+        <v>2.8814</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. FERNANDEZ</t>
+          <t>G. SHERMADINI</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>7.2777</v>
+        <v>6.1079</v>
       </c>
       <c r="E3" t="n">
-        <v>6.2744</v>
+        <v>8.4351</v>
       </c>
       <c r="F3" t="n">
-        <v>1.0033</v>
+        <v>-2.3272</v>
       </c>
       <c r="G3" t="n">
-        <v>3.6842</v>
+        <v>2.1035</v>
       </c>
       <c r="H3" t="n">
-        <v>1.7331</v>
+        <v>1.911</v>
       </c>
       <c r="I3" t="n">
-        <v>1.9511</v>
+        <v>0.1925</v>
       </c>
       <c r="J3" t="n">
-        <v>4.0776</v>
+        <v>4.683</v>
       </c>
       <c r="K3" t="n">
-        <v>1.7348</v>
+        <v>3.3053</v>
       </c>
       <c r="L3" t="n">
-        <v>2.3428</v>
+        <v>1.3778</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.3935</v>
+        <v>-2.5795</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.0017</v>
+        <v>-1.3943</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.3918</v>
+        <v>-1.1852</v>
       </c>
       <c r="P3" t="n">
-        <v>1.8147</v>
+        <v>0.2276</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.2268</v>
+        <v>-1.3658</v>
       </c>
       <c r="R3" t="n">
-        <v>2.0415</v>
+        <v>1.5934</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.0209</v>
+        <v>0.8953</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.4688</v>
+        <v>1.1469</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4479</v>
+        <v>-0.2516</v>
       </c>
       <c r="V3" t="n">
-        <v>1.7997</v>
+        <v>2.8814</v>
       </c>
       <c r="W3" t="n">
-        <v>2.8924</v>
+        <v>3.9709</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="4">
@@ -721,58 +721,58 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.02</v>
+        <v>4.7291</v>
       </c>
       <c r="E4" t="n">
-        <v>2.322</v>
+        <v>3.4948</v>
       </c>
       <c r="F4" t="n">
-        <v>0.6979</v>
+        <v>1.2343</v>
       </c>
       <c r="G4" t="n">
         <v>2.6316</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.7029</v>
+        <v>-0.6927</v>
       </c>
       <c r="I4" t="n">
-        <v>3.3345</v>
+        <v>3.3244</v>
       </c>
       <c r="J4" t="n">
-        <v>3.435</v>
+        <v>3.4046</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.2913</v>
+        <v>-0.3038</v>
       </c>
       <c r="L4" t="n">
-        <v>3.7263</v>
+        <v>3.7083</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.8034</v>
+        <v>-0.7729</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.4116</v>
+        <v>-0.389</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.3918</v>
+        <v>-0.384</v>
       </c>
       <c r="P4" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.6532</v>
+        <v>0.0487</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.113</v>
+        <v>0.0902</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.5402</v>
+        <v>-0.0414</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -799,58 +799,58 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.8253</v>
+        <v>3.1853</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.1159</v>
+        <v>0.3431</v>
       </c>
       <c r="F5" t="n">
-        <v>2.9411</v>
+        <v>2.8421</v>
       </c>
       <c r="G5" t="n">
-        <v>1.6717</v>
+        <v>1.6801</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6189</v>
+        <v>0.6284999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>1.0529</v>
+        <v>1.0516</v>
       </c>
       <c r="J5" t="n">
-        <v>1.4175</v>
+        <v>1.4072</v>
       </c>
       <c r="K5" t="n">
-        <v>0.9351</v>
+        <v>0.9308</v>
       </c>
       <c r="L5" t="n">
-        <v>0.4824</v>
+        <v>0.4764</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2542</v>
+        <v>0.2729</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.3162</v>
+        <v>-0.3023</v>
       </c>
       <c r="O5" t="n">
-        <v>0.5705</v>
+        <v>0.5752</v>
       </c>
       <c r="P5" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R5" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S5" t="n">
-        <v>0.473</v>
+        <v>0.8223</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.3992</v>
+        <v>0.0741</v>
       </c>
       <c r="U5" t="n">
-        <v>0.8722</v>
+        <v>0.7482</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>F. GUERRA</t>
+          <t>R. GIEDRAITIS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.5159</v>
+        <v>1.9847</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.06469999999999999</v>
+        <v>2.1014</v>
       </c>
       <c r="F6" t="n">
-        <v>2.5806</v>
+        <v>-0.1167</v>
       </c>
       <c r="G6" t="n">
-        <v>1.771</v>
+        <v>0.5711000000000001</v>
       </c>
       <c r="H6" t="n">
-        <v>0.9046999999999999</v>
+        <v>1.3492</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8663</v>
+        <v>-0.778</v>
       </c>
       <c r="J6" t="n">
-        <v>1.0482</v>
+        <v>2.3061</v>
       </c>
       <c r="K6" t="n">
-        <v>0.3392</v>
+        <v>2.0684</v>
       </c>
       <c r="L6" t="n">
-        <v>0.709</v>
+        <v>0.2377</v>
       </c>
       <c r="M6" t="n">
-        <v>0.7228</v>
+        <v>-1.735</v>
       </c>
       <c r="N6" t="n">
-        <v>0.5655</v>
+        <v>-0.7193000000000001</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1573</v>
+        <v>-1.0157</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.4537</v>
+        <v>1.1382</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.2683</v>
+        <v>-1.3658</v>
       </c>
       <c r="R6" t="n">
-        <v>1.8147</v>
+        <v>2.5039</v>
       </c>
       <c r="S6" t="n">
-        <v>2.4519</v>
+        <v>0.4332</v>
       </c>
       <c r="T6" t="n">
-        <v>1.1553</v>
+        <v>0.0717</v>
       </c>
       <c r="U6" t="n">
-        <v>1.2966</v>
+        <v>0.3616</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.2534</v>
+        <v>-0.1578</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.0895</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.2534</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>R. GIEDRAITIS</t>
+          <t>F. GUERRA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.8172</v>
+        <v>1.1652</v>
       </c>
       <c r="E7" t="n">
-        <v>1.9448</v>
+        <v>-0.9061</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.1277</v>
+        <v>2.0713</v>
       </c>
       <c r="G7" t="n">
-        <v>0.5682</v>
+        <v>1.7701</v>
       </c>
       <c r="H7" t="n">
-        <v>1.336</v>
+        <v>0.9046999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.7678</v>
+        <v>0.8653999999999999</v>
       </c>
       <c r="J7" t="n">
-        <v>2.3311</v>
+        <v>1.0383</v>
       </c>
       <c r="K7" t="n">
-        <v>2.078</v>
+        <v>0.3308</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2531</v>
+        <v>0.7075</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.7629</v>
+        <v>0.7319</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.742</v>
+        <v>0.574</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.0209</v>
+        <v>0.1579</v>
       </c>
       <c r="P7" t="n">
-        <v>1.1342</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.361</v>
+        <v>-2.2763</v>
       </c>
       <c r="R7" t="n">
-        <v>2.4952</v>
+        <v>1.8211</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2755</v>
+        <v>1.0976</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1179</v>
+        <v>0.3319</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3935</v>
+        <v>0.7655999999999999</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.1607</v>
+        <v>-1.2472</v>
       </c>
       <c r="W7" t="n">
-        <v>1.0927</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.2534</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="8">
@@ -1033,64 +1033,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4812</v>
+        <v>0.7737000000000001</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.6885</v>
+        <v>-0.511</v>
       </c>
       <c r="F8" t="n">
-        <v>1.1697</v>
+        <v>1.2847</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.9836</v>
+        <v>-1.9754</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.4532</v>
+        <v>-1.4451</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.5304</v>
+        <v>-0.5303</v>
       </c>
       <c r="J8" t="n">
-        <v>-2.2379</v>
+        <v>-2.2483</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.6651</v>
+        <v>-0.669</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.5727</v>
+        <v>-1.5793</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2542</v>
+        <v>0.2729</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.788</v>
+        <v>-0.7761</v>
       </c>
       <c r="O8" t="n">
-        <v>1.0423</v>
+        <v>1.049</v>
       </c>
       <c r="P8" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S8" t="n">
-        <v>0.4649</v>
+        <v>0.7491</v>
       </c>
       <c r="T8" t="n">
-        <v>0.4567</v>
+        <v>0.6478</v>
       </c>
       <c r="U8" t="n">
-        <v>0.008200000000000001</v>
+        <v>0.1013</v>
       </c>
       <c r="V8" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W8" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
@@ -1111,58 +1111,58 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1762</v>
+        <v>0.5394</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.0198</v>
+        <v>0.4487</v>
       </c>
       <c r="F9" t="n">
-        <v>0.196</v>
+        <v>0.09080000000000001</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.1345</v>
+        <v>-1.1237</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.4864</v>
+        <v>-1.4768</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3519</v>
+        <v>0.3531</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1012</v>
+        <v>0.0958</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.6825</v>
+        <v>-0.6862</v>
       </c>
       <c r="L9" t="n">
-        <v>0.7837</v>
+        <v>0.782</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.2357</v>
+        <v>-1.2194</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.8038999999999999</v>
+        <v>-0.7906</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.4318</v>
+        <v>-0.4289</v>
       </c>
       <c r="P9" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S9" t="n">
-        <v>0.1766</v>
+        <v>0.525</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.121</v>
+        <v>0.3529</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2976</v>
+        <v>0.1721</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,22 +1189,22 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.1573</v>
+        <v>0.1579</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1573</v>
+        <v>0.1579</v>
       </c>
       <c r="G10" t="n">
-        <v>0.1573</v>
+        <v>0.1579</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1573</v>
+        <v>0.1579</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1216,13 +1216,13 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>0.1573</v>
+        <v>0.1579</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>0.1573</v>
+        <v>0.1579</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.0409</v>
+        <v>-1.8555</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.9423</v>
+        <v>-0.8273</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.0986</v>
+        <v>-1.0282</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.0131</v>
+        <v>-0.008800000000000001</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.3276</v>
+        <v>-0.3247</v>
       </c>
       <c r="I11" t="n">
-        <v>0.3145</v>
+        <v>0.3159</v>
       </c>
       <c r="J11" t="n">
-        <v>0.0346</v>
+        <v>0.0345</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0346</v>
+        <v>0.0345</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.0477</v>
+        <v>-0.0433</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.3622</v>
+        <v>-0.3592</v>
       </c>
       <c r="O11" t="n">
-        <v>0.3145</v>
+        <v>0.3159</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>0.199</v>
+        <v>0.3809</v>
       </c>
       <c r="T11" t="n">
-        <v>0.1573</v>
+        <v>0.2764</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0417</v>
+        <v>0.1046</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.3086</v>
+        <v>-2.7721</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.689</v>
+        <v>-1.0954</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.6196</v>
+        <v>-1.6767</v>
       </c>
       <c r="G12" t="n">
-        <v>-4.046</v>
+        <v>-4.0308</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.9859</v>
+        <v>-0.9634</v>
       </c>
       <c r="I12" t="n">
-        <v>-3.0601</v>
+        <v>-3.0674</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.505</v>
+        <v>-1.5223</v>
       </c>
       <c r="K12" t="n">
-        <v>0.2598</v>
+        <v>0.2586</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.7647</v>
+        <v>-1.7808</v>
       </c>
       <c r="M12" t="n">
-        <v>-2.541</v>
+        <v>-2.5086</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.2457</v>
+        <v>-1.2219</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.2954</v>
+        <v>-1.2866</v>
       </c>
       <c r="P12" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R12" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.238</v>
+        <v>0.2799</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.1179</v>
+        <v>0.4967</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1201</v>
+        <v>-0.2168</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.3856</v>
+        <v>-0.387</v>
       </c>
       <c r="W12" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-5.7905</v>
+        <v>-6.6451</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.8842</v>
+        <v>-3.6543</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.9063</v>
+        <v>-2.9908</v>
       </c>
       <c r="G13" t="n">
-        <v>-3.0725</v>
+        <v>-3.0926</v>
       </c>
       <c r="H13" t="n">
-        <v>-3.5363</v>
+        <v>-3.5574</v>
       </c>
       <c r="I13" t="n">
-        <v>0.4638</v>
+        <v>0.4648</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.5155999999999999</v>
+        <v>-0.5695</v>
       </c>
       <c r="K13" t="n">
-        <v>-2.1175</v>
+        <v>-2.1631</v>
       </c>
       <c r="L13" t="n">
-        <v>1.6019</v>
+        <v>1.5935</v>
       </c>
       <c r="M13" t="n">
-        <v>-2.5569</v>
+        <v>-2.523</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.4188</v>
+        <v>-1.3943</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.1381</v>
+        <v>-1.1287</v>
       </c>
       <c r="P13" t="n">
-        <v>-5.444</v>
+        <v>-5.4632</v>
       </c>
       <c r="Q13" t="n">
-        <v>-7.0318</v>
+        <v>-7.0566</v>
       </c>
       <c r="R13" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S13" t="n">
-        <v>1.087</v>
+        <v>0.2764</v>
       </c>
       <c r="T13" t="n">
-        <v>1.3852</v>
+        <v>0.7034</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.2982</v>
+        <v>-0.427</v>
       </c>
       <c r="V13" t="n">
-        <v>1.639</v>
+        <v>1.6342</v>
       </c>
       <c r="W13" t="n">
-        <v>3.278</v>
+        <v>3.2684</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.639</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="14">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>14.9092</v>
+        <v>15.621</v>
       </c>
       <c r="E14" t="n">
-        <v>14.3783</v>
+        <v>14.76</v>
       </c>
       <c r="F14" t="n">
-        <v>0.5306000000000006</v>
+        <v>0.8609999999999989</v>
       </c>
       <c r="G14" t="n">
-        <v>2.3478</v>
+        <v>2.3484</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.9701</v>
+        <v>-1.9402</v>
       </c>
       <c r="I14" t="n">
-        <v>4.318</v>
+        <v>4.288799999999999</v>
       </c>
       <c r="J14" t="n">
-        <v>12.9158</v>
+        <v>12.6653</v>
       </c>
       <c r="K14" t="n">
-        <v>4.9734</v>
+        <v>4.8193</v>
       </c>
       <c r="L14" t="n">
-        <v>7.942500000000001</v>
+        <v>7.846</v>
       </c>
       <c r="M14" t="n">
-        <v>-10.5681</v>
+        <v>-10.3165</v>
       </c>
       <c r="N14" t="n">
-        <v>-6.9434</v>
+        <v>-6.7595</v>
       </c>
       <c r="O14" t="n">
-        <v>-3.6246</v>
+        <v>-3.5572</v>
       </c>
       <c r="P14" t="n">
-        <v>2.268300000000001</v>
+        <v>2.276300000000001</v>
       </c>
       <c r="Q14" t="n">
-        <v>-14.7441</v>
+        <v>-14.7961</v>
       </c>
       <c r="R14" t="n">
-        <v>17.0125</v>
+        <v>17.0724</v>
       </c>
       <c r="S14" t="n">
-        <v>5.7615</v>
+        <v>6.4805</v>
       </c>
       <c r="T14" t="n">
-        <v>3.7051</v>
+        <v>4.4333</v>
       </c>
       <c r="U14" t="n">
-        <v>2.0565</v>
+        <v>2.0474</v>
       </c>
       <c r="V14" t="n">
-        <v>4.5314</v>
+        <v>4.5156</v>
       </c>
       <c r="W14" t="n">
-        <v>12.5016</v>
+        <v>12.4575</v>
       </c>
       <c r="X14" t="n">
-        <v>-7.970199999999999</v>
+        <v>-7.9418</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. GASPA</t>
+          <t>A. PLUMMER</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.1485</v>
+        <v>2.2845</v>
       </c>
       <c r="E15" t="n">
-        <v>3.1967</v>
+        <v>2.5787</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.0482</v>
+        <v>-0.2943</v>
       </c>
       <c r="G15" t="n">
-        <v>2.1542</v>
+        <v>2.0169</v>
       </c>
       <c r="H15" t="n">
-        <v>2.7273</v>
+        <v>-0.9364</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.5731000000000001</v>
+        <v>2.9533</v>
       </c>
       <c r="J15" t="n">
-        <v>2.8973</v>
+        <v>2.1585</v>
       </c>
       <c r="K15" t="n">
-        <v>2.8226</v>
+        <v>-0.6485</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0746</v>
+        <v>2.807</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.7431</v>
+        <v>-0.1416</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.0954</v>
+        <v>-0.2879</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.6477000000000001</v>
+        <v>0.1463</v>
       </c>
       <c r="P15" t="n">
-        <v>1.1342</v>
+        <v>1.5934</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-0.2276</v>
       </c>
       <c r="R15" t="n">
-        <v>1.1342</v>
+        <v>1.8211</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.0472</v>
+        <v>-1.0592</v>
       </c>
       <c r="T15" t="n">
-        <v>0.2994</v>
+        <v>-0.4416</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.3466</v>
+        <v>-0.6176</v>
       </c>
       <c r="V15" t="n">
-        <v>-1.0927</v>
+        <v>-0.2667</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.0895</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.0927</v>
+        <v>-1.3562</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>L. OLINDE</t>
+          <t>M. GASPA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.9897</v>
+        <v>2.2654</v>
       </c>
       <c r="E16" t="n">
-        <v>1.3526</v>
+        <v>2.9489</v>
       </c>
       <c r="F16" t="n">
-        <v>0.6371</v>
+        <v>-0.6835</v>
       </c>
       <c r="G16" t="n">
-        <v>0.7685</v>
+        <v>2.1541</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.6495</v>
+        <v>2.723</v>
       </c>
       <c r="I16" t="n">
-        <v>1.418</v>
+        <v>-0.5688</v>
       </c>
       <c r="J16" t="n">
-        <v>1.3828</v>
+        <v>2.8841</v>
       </c>
       <c r="K16" t="n">
-        <v>0.0448</v>
+        <v>2.8096</v>
       </c>
       <c r="L16" t="n">
-        <v>1.338</v>
+        <v>0.0745</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.6143</v>
+        <v>-0.73</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.6944</v>
+        <v>-0.0866</v>
       </c>
       <c r="O16" t="n">
-        <v>0.08</v>
+        <v>-0.6433</v>
       </c>
       <c r="P16" t="n">
-        <v>1.8147</v>
+        <v>1.1382</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.8147</v>
+        <v>1.1382</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.4328</v>
+        <v>0.0626</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.0302</v>
+        <v>0.0648</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.4026</v>
+        <v>-0.0022</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.1607</v>
+        <v>-1.0895</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.1607</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. PLUMMER</t>
+          <t>L. OLINDE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.8047</v>
+        <v>2.195</v>
       </c>
       <c r="E17" t="n">
-        <v>2.3787</v>
+        <v>1.3346</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.5741000000000001</v>
+        <v>0.8604000000000001</v>
       </c>
       <c r="G17" t="n">
-        <v>2.0287</v>
+        <v>0.7768</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.9379</v>
+        <v>-0.6382</v>
       </c>
       <c r="I17" t="n">
-        <v>2.9666</v>
+        <v>1.415</v>
       </c>
       <c r="J17" t="n">
-        <v>2.1903</v>
+        <v>1.3629</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.6375999999999999</v>
+        <v>0.0377</v>
       </c>
       <c r="L17" t="n">
-        <v>2.828</v>
+        <v>1.3252</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.1617</v>
+        <v>-0.5861</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.3003</v>
+        <v>-0.6758999999999999</v>
       </c>
       <c r="O17" t="n">
-        <v>0.1387</v>
+        <v>0.0898</v>
       </c>
       <c r="P17" t="n">
-        <v>1.5878</v>
+        <v>1.8211</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.2268</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.5419</v>
+        <v>-0.2451</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.6775</v>
+        <v>-0.0283</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.8643999999999999</v>
+        <v>-0.2168</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.27</v>
+        <v>-0.1578</v>
       </c>
       <c r="W17" t="n">
-        <v>1.0927</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.3627</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="18">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.0781</v>
+        <v>0.3852</v>
       </c>
       <c r="E18" t="n">
-        <v>1.6219</v>
+        <v>1.0843</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.5438</v>
+        <v>-0.6991000000000001</v>
       </c>
       <c r="G18" t="n">
-        <v>0.9053</v>
+        <v>0.8763</v>
       </c>
       <c r="H18" t="n">
-        <v>0.836</v>
+        <v>0.8031</v>
       </c>
       <c r="I18" t="n">
-        <v>0.0693</v>
+        <v>0.0732</v>
       </c>
       <c r="J18" t="n">
-        <v>2.8841</v>
+        <v>2.8257</v>
       </c>
       <c r="K18" t="n">
-        <v>2.3644</v>
+        <v>2.312</v>
       </c>
       <c r="L18" t="n">
-        <v>0.5197000000000001</v>
+        <v>0.5135999999999999</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.9788</v>
+        <v>-1.9494</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.5284</v>
+        <v>-1.5089</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.4504</v>
+        <v>-0.4405</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.4952</v>
+        <v>-2.5039</v>
       </c>
       <c r="R18" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S18" t="n">
-        <v>0.4162</v>
+        <v>-0.244</v>
       </c>
       <c r="T18" t="n">
-        <v>0.6866</v>
+        <v>0.2179</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2704</v>
+        <v>-0.4618</v>
       </c>
       <c r="V18" t="n">
-        <v>0.4371</v>
+        <v>0.4358</v>
       </c>
       <c r="W18" t="n">
-        <v>0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.1093</v>
+        <v>-0.1089</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>K. AKOBUNDU</t>
+          <t>A. UBAL</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.5603</v>
+        <v>-0.5145</v>
       </c>
       <c r="E19" t="n">
-        <v>0.4486</v>
+        <v>1.0618</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.0089</v>
+        <v>-1.5764</v>
       </c>
       <c r="G19" t="n">
-        <v>3.1768</v>
+        <v>-2.0196</v>
       </c>
       <c r="H19" t="n">
-        <v>1.5455</v>
+        <v>-1.6459</v>
       </c>
       <c r="I19" t="n">
-        <v>1.6313</v>
+        <v>-0.3737</v>
       </c>
       <c r="J19" t="n">
-        <v>2.7653</v>
+        <v>-1.2607</v>
       </c>
       <c r="K19" t="n">
-        <v>2.019</v>
+        <v>-1.3724</v>
       </c>
       <c r="L19" t="n">
-        <v>0.7463</v>
+        <v>0.1117</v>
       </c>
       <c r="M19" t="n">
-        <v>0.4115</v>
+        <v>-0.7588</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.4735</v>
+        <v>-0.2734</v>
       </c>
       <c r="O19" t="n">
-        <v>0.885</v>
+        <v>-0.4854</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.4537</v>
+        <v>1.3658</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.4952</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>2.0415</v>
+        <v>1.3658</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.4425</v>
+        <v>-0.0185</v>
       </c>
       <c r="T19" t="n">
-        <v>0.1785</v>
+        <v>-0.0141</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.6209</v>
+        <v>-0.0044</v>
       </c>
       <c r="V19" t="n">
-        <v>-2.8409</v>
+        <v>0.1578</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>2.3367</v>
       </c>
       <c r="X19" t="n">
-        <v>-2.8409</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. UBAL</t>
+          <t>K. AKOBUNDU</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.7456</v>
+        <v>-0.8146</v>
       </c>
       <c r="E20" t="n">
-        <v>0.6062</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.3518</v>
+        <v>-0.8836000000000001</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.0278</v>
+        <v>3.1783</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.6494</v>
+        <v>1.5425</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.3785</v>
+        <v>1.6358</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.253</v>
+        <v>2.7475</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.3649</v>
+        <v>2.0027</v>
       </c>
       <c r="L20" t="n">
-        <v>0.112</v>
+        <v>0.7447</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.7749</v>
+        <v>0.4308</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.2844</v>
+        <v>-0.4603</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.4904</v>
+        <v>0.8911</v>
       </c>
       <c r="P20" t="n">
-        <v>1.361</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-2.5039</v>
       </c>
       <c r="R20" t="n">
-        <v>1.361</v>
+        <v>2.0487</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.2395</v>
+        <v>-0.705</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.4869</v>
+        <v>-0.1745</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2474</v>
+        <v>-0.5304</v>
       </c>
       <c r="V20" t="n">
-        <v>0.1607</v>
+        <v>-2.8326</v>
       </c>
       <c r="W20" t="n">
-        <v>2.3461</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-2.1853</v>
+        <v>-2.8326</v>
       </c>
     </row>
     <row r="21">
@@ -2047,58 +2047,58 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.5779</v>
+        <v>-1.0741</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.5347</v>
+        <v>-0.4285</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.0432</v>
+        <v>-0.6456</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.3066</v>
+        <v>-1.2982</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.6856</v>
+        <v>-0.6755</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.6211</v>
+        <v>-0.6227</v>
       </c>
       <c r="J21" t="n">
-        <v>0.2304</v>
+        <v>0.2198</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.6998</v>
+        <v>-0.7035</v>
       </c>
       <c r="L21" t="n">
-        <v>0.9302</v>
+        <v>0.9233</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.5371</v>
+        <v>-1.518</v>
       </c>
       <c r="N21" t="n">
-        <v>0.0142</v>
+        <v>0.028</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.5513</v>
+        <v>-1.546</v>
       </c>
       <c r="P21" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.4055</v>
+        <v>-0.9141</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.7652</v>
+        <v>-0.6483</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.6403</v>
+        <v>-0.2658</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.8184</v>
+        <v>-1.6564</v>
       </c>
       <c r="E22" t="n">
-        <v>0.3838</v>
+        <v>0.3255</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.2022</v>
+        <v>-1.9819</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.09420000000000001</v>
+        <v>-0.1152</v>
       </c>
       <c r="H22" t="n">
-        <v>1.1852</v>
+        <v>1.1534</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.2794</v>
+        <v>-1.2687</v>
       </c>
       <c r="J22" t="n">
-        <v>1.6078</v>
+        <v>1.5591</v>
       </c>
       <c r="K22" t="n">
-        <v>1.5332</v>
+        <v>1.4847</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0746</v>
+        <v>0.0745</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.702</v>
+        <v>-1.6744</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.348</v>
+        <v>-0.3312</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.354</v>
+        <v>-1.3432</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R22" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.3632</v>
+        <v>-0.1754</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.0484</v>
+        <v>-0.0468</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.3149</v>
+        <v>-0.1286</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="23">
@@ -2203,22 +2203,22 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.3232</v>
+        <v>-2.325</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.2037</v>
+        <v>-1.2079</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.1195</v>
+        <v>-1.1171</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.1195</v>
+        <v>-1.1171</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.1195</v>
+        <v>-1.1171</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2230,28 +2230,28 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.1195</v>
+        <v>-1.1171</v>
       </c>
       <c r="N23" t="n">
         <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.1195</v>
+        <v>-1.1171</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.0696</v>
+        <v>-0.0697</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.0696</v>
+        <v>-0.0697</v>
       </c>
       <c r="U23" t="n">
         <v>0</v>
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.0432</v>
+        <v>-3.7366</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.35</v>
+        <v>-2.6089</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.6931</v>
+        <v>-1.1277</v>
       </c>
       <c r="G24" t="n">
-        <v>-4.8</v>
+        <v>-4.7917</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.3348</v>
+        <v>-1.33</v>
       </c>
       <c r="I24" t="n">
-        <v>-3.4652</v>
+        <v>-3.4617</v>
       </c>
       <c r="J24" t="n">
-        <v>-2.7089</v>
+        <v>-2.7306</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.4991</v>
+        <v>-0.5106000000000001</v>
       </c>
       <c r="L24" t="n">
-        <v>-2.2098</v>
+        <v>-2.22</v>
       </c>
       <c r="M24" t="n">
-        <v>-2.0911</v>
+        <v>-2.0612</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.8357</v>
+        <v>-0.8194</v>
       </c>
       <c r="O24" t="n">
-        <v>-1.2554</v>
+        <v>-1.2417</v>
       </c>
       <c r="P24" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q24" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R24" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S24" t="n">
-        <v>0.3463</v>
+        <v>-0.3611</v>
       </c>
       <c r="T24" t="n">
-        <v>0.0393</v>
+        <v>-0.1955</v>
       </c>
       <c r="U24" t="n">
-        <v>0.307</v>
+        <v>-0.1656</v>
       </c>
       <c r="V24" t="n">
-        <v>0.2763</v>
+        <v>0.278</v>
       </c>
       <c r="W24" t="n">
-        <v>0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.27</v>
+        <v>-0.2667</v>
       </c>
     </row>
     <row r="25">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-4.8189</v>
+        <v>-4.5187</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.2339</v>
+        <v>-0.0233</v>
       </c>
       <c r="F25" t="n">
-        <v>-4.5851</v>
+        <v>-4.4954</v>
       </c>
       <c r="G25" t="n">
-        <v>0.2186</v>
+        <v>0.227</v>
       </c>
       <c r="H25" t="n">
-        <v>1.2928</v>
+        <v>1.2979</v>
       </c>
       <c r="I25" t="n">
-        <v>-1.0742</v>
+        <v>-1.0709</v>
       </c>
       <c r="J25" t="n">
-        <v>1.268</v>
+        <v>1.2568</v>
       </c>
       <c r="K25" t="n">
-        <v>1.42</v>
+        <v>1.4134</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.152</v>
+        <v>-0.1566</v>
       </c>
       <c r="M25" t="n">
-        <v>-1.0494</v>
+        <v>-1.0298</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.1272</v>
+        <v>-0.1155</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.9222</v>
+        <v>-0.9143</v>
       </c>
       <c r="P25" t="n">
-        <v>-2.0415</v>
+        <v>-2.0487</v>
       </c>
       <c r="Q25" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R25" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.9715</v>
+        <v>-0.6758</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.4869</v>
+        <v>-0.251</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.4845</v>
+        <v>-0.4248</v>
       </c>
       <c r="V25" t="n">
-        <v>-2.0246</v>
+        <v>-2.0212</v>
       </c>
       <c r="W25" t="n">
-        <v>1.2534</v>
+        <v>1.2472</v>
       </c>
       <c r="X25" t="n">
-        <v>-3.278</v>
+        <v>-3.2684</v>
       </c>
     </row>
     <row r="26">
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-7.0424</v>
+        <v>-6.6244</v>
       </c>
       <c r="E26" t="n">
-        <v>-6.1967</v>
+        <v>-5.9955</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.8456</v>
+        <v>-0.629</v>
       </c>
       <c r="G26" t="n">
-        <v>-2.2518</v>
+        <v>-2.236</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.3594</v>
+        <v>-0.3536</v>
       </c>
       <c r="I26" t="n">
-        <v>-1.8924</v>
+        <v>-1.8824</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.6961000000000001</v>
+        <v>-0.7064</v>
       </c>
       <c r="K26" t="n">
-        <v>-0.0591</v>
+        <v>-0.06569999999999999</v>
       </c>
       <c r="L26" t="n">
-        <v>-0.6371</v>
+        <v>-0.6407</v>
       </c>
       <c r="M26" t="n">
-        <v>-1.5557</v>
+        <v>-1.5296</v>
       </c>
       <c r="N26" t="n">
-        <v>-0.3003</v>
+        <v>-0.2879</v>
       </c>
       <c r="O26" t="n">
-        <v>-1.2554</v>
+        <v>-1.2417</v>
       </c>
       <c r="P26" t="n">
-        <v>-4.7635</v>
+        <v>-4.7803</v>
       </c>
       <c r="Q26" t="n">
-        <v>-5.8976</v>
+        <v>-5.9184</v>
       </c>
       <c r="R26" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S26" t="n">
-        <v>-1.0105</v>
+        <v>-0.5887</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.6956</v>
+        <v>-0.4601</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.3149</v>
+        <v>-0.1286</v>
       </c>
       <c r="V26" t="n">
-        <v>0.9834000000000001</v>
+        <v>0.9805</v>
       </c>
       <c r="W26" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X26" t="n">
-        <v>-0.1093</v>
+        <v>-0.1089</v>
       </c>
     </row>
     <row r="27">
@@ -2515,67 +2515,67 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-14.9089</v>
+        <v>-14.1342</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.5305</v>
+        <v>-0.8613000000000008</v>
       </c>
       <c r="F27" t="n">
-        <v>-14.3784</v>
+        <v>-13.2732</v>
       </c>
       <c r="G27" t="n">
-        <v>-2.347799999999999</v>
+        <v>-2.348399999999999</v>
       </c>
       <c r="H27" t="n">
-        <v>1.9702</v>
+        <v>1.9403</v>
       </c>
       <c r="I27" t="n">
-        <v>-4.3182</v>
+        <v>-4.2887</v>
       </c>
       <c r="J27" t="n">
-        <v>10.568</v>
+        <v>10.3167</v>
       </c>
       <c r="K27" t="n">
-        <v>6.943499999999999</v>
+        <v>6.7594</v>
       </c>
       <c r="L27" t="n">
-        <v>3.6245</v>
+        <v>3.5572</v>
       </c>
       <c r="M27" t="n">
-        <v>-12.9161</v>
+        <v>-12.6652</v>
       </c>
       <c r="N27" t="n">
-        <v>-4.9734</v>
+        <v>-4.818999999999999</v>
       </c>
       <c r="O27" t="n">
-        <v>-7.942600000000001</v>
+        <v>-7.845999999999999</v>
       </c>
       <c r="P27" t="n">
-        <v>-2.268299999999999</v>
+        <v>-2.276300000000001</v>
       </c>
       <c r="Q27" t="n">
-        <v>-17.0124</v>
+        <v>-17.0722</v>
       </c>
       <c r="R27" t="n">
-        <v>14.7443</v>
+        <v>14.7963</v>
       </c>
       <c r="S27" t="n">
-        <v>-5.761700000000001</v>
+        <v>-4.994000000000001</v>
       </c>
       <c r="T27" t="n">
-        <v>-2.0565</v>
+        <v>-2.0472</v>
       </c>
       <c r="U27" t="n">
-        <v>-3.7051</v>
+        <v>-2.9466</v>
       </c>
       <c r="V27" t="n">
-        <v>-4.5314</v>
+        <v>-4.5157</v>
       </c>
       <c r="W27" t="n">
-        <v>7.9702</v>
+        <v>7.9418</v>
       </c>
       <c r="X27" t="n">
-        <v>-12.5016</v>
+        <v>-12.4574</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104461_W1.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104461_W1.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X27"/>
+  <dimension ref="A1:Y27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104461_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104461_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104461_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>0</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104461_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104461_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104461_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>0</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104461_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>0</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104461_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>0</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104461_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104461_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104461_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,11 @@
       <c r="X13" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_104461_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1628,7 @@
       <c r="X14" t="n">
         <v>-7.9418</v>
       </c>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-1.3562</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104461_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104461_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104461_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>-0.1089</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104461_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104461_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>-2.8326</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104461_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>0</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104461_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104461_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>0</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104461_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>-0.2667</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104461_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,11 @@
       <c r="X25" t="n">
         <v>-3.2684</v>
       </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_104461_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2499,6 +2620,11 @@
       <c r="X26" t="n">
         <v>-0.1089</v>
       </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>play_by_play_104461_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2577,6 +2703,7 @@
       <c r="X27" t="n">
         <v>-12.4574</v>
       </c>
+      <c r="Y27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
